--- a/差异化城市设计/计算-光伏阵列-拉萨.xlsx
+++ b/差异化城市设计/计算-光伏阵列-拉萨.xlsx
@@ -456,8 +456,6 @@
           <t>PV array design inputs (Lhasa W5)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -633,7 +631,6 @@
       <c r="B14" t="n">
         <v>44.12</v>
       </c>
-      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -644,7 +641,6 @@
       <c r="B15" t="n">
         <v>14.49</v>
       </c>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -655,7 +651,6 @@
       <c r="B16" t="n">
         <v>13.6</v>
       </c>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -666,7 +661,6 @@
       <c r="B17" t="n">
         <v>-0.0023</v>
       </c>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -677,7 +671,6 @@
       <c r="B18" t="n">
         <v>-0.0028</v>
       </c>
-      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -688,7 +681,6 @@
       <c r="B19" t="n">
         <v>600</v>
       </c>
-      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -714,7 +706,6 @@
       <c r="B21" t="n">
         <v>430</v>
       </c>
-      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -725,7 +716,6 @@
       <c r="B22" t="n">
         <v>450</v>
       </c>
-      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -736,7 +726,6 @@
       <c r="B23" t="n">
         <v>22</v>
       </c>
-      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -747,7 +736,6 @@
       <c r="B24" t="n">
         <v>6000</v>
       </c>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -758,7 +746,6 @@
       <c r="B25" t="n">
         <v>5</v>
       </c>
-      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -769,7 +756,6 @@
       <c r="B26" t="n">
         <v>1</v>
       </c>
-      <c r="C26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -820,9 +806,10 @@
           <t>P_PV,min (kWp)</t>
         </is>
       </c>
-      <c r="B2">
-        <f>E_AC*K_PV/(H_tilt*eta_path)</f>
-        <v/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>E_AC*K_PV/(H_tilt*eta_path)</t>
+        </is>
       </c>
       <c r="C2">
         <f>Parameters!B3*Parameters!B4/(Parameters!B5*Parameters!B6)</f>
@@ -840,9 +827,10 @@
           <t>Voc,cold (V)</t>
         </is>
       </c>
-      <c r="B3">
-        <f>Voc_STC*(1+beta_Voc*(T_min-25))</f>
-        <v/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Voc_STC*(1+beta_Voc*(T_min-25))</t>
+        </is>
       </c>
       <c r="C3">
         <f>Parameters!B13*(1+Parameters!B17*(Parameters!B7-25))</f>
@@ -860,9 +848,10 @@
           <t>Vmp,hot extreme (V)</t>
         </is>
       </c>
-      <c r="B4">
-        <f>Vmp_STC*(1+beta_Vmp*(Tc_ext-25))</f>
-        <v/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Vmp_STC*(1+beta_Vmp*(Tc_ext-25))</t>
+        </is>
       </c>
       <c r="C4">
         <f>Parameters!B14*(1+Parameters!B18*(Parameters!B8-25))</f>
@@ -880,9 +869,10 @@
           <t>Vmp,hot normal (V)</t>
         </is>
       </c>
-      <c r="B5">
-        <f>Vmp_STC*(1+beta_Vmp*(Tc_norm-25))</f>
-        <v/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Vmp_STC*(1+beta_Vmp*(Tc_norm-25))</t>
+        </is>
       </c>
       <c r="C5">
         <f>Parameters!B14*(1+Parameters!B18*(Parameters!B9-25))</f>
@@ -900,9 +890,10 @@
           <t>Vmp,cold (V)</t>
         </is>
       </c>
-      <c r="B6">
-        <f>Vmp_STC*(1+beta_Vmp*(T_min-25))</f>
-        <v/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Vmp_STC*(1+beta_Vmp*(T_min-25))</t>
+        </is>
       </c>
       <c r="C6">
         <f>Parameters!B14*(1+Parameters!B18*(Parameters!B7-25))</f>
@@ -920,9 +911,10 @@
           <t>N_S,min</t>
         </is>
       </c>
-      <c r="B7">
-        <f>CEILING(V_MPPT_min/Vmp_hot_ext,1)</f>
-        <v/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CEILING(V_MPPT_min/Vmp_hot_ext,1)</t>
+        </is>
       </c>
       <c r="C7">
         <f>CEILING(Parameters!B20/C4,1)</f>
@@ -940,13 +932,15 @@
           <t>N_S,max</t>
         </is>
       </c>
-      <c r="B8">
-        <f>FLOOR(V_ctrl_max/Voc_cold,1)</f>
-        <v/>
-      </c>
-      <c r="C8">
-        <f>FLOOR(Parameters!B22/C3,1)</f>
-        <v/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FLOOR(V_ctrl_max/Voc_cold,1)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FLOOR(Parameters!B22/C3,1)</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -960,9 +954,10 @@
           <t>Actual P_PV (kWp)</t>
         </is>
       </c>
-      <c r="B9">
-        <f>N_S*N_P*P_mod/1000</f>
-        <v/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N_S*N_P*P_mod/1000</t>
+        </is>
       </c>
       <c r="C9">
         <f>Parameters!B25*Parameters!B26*Parameters!B19/1000</f>
@@ -980,9 +975,10 @@
           <t>String Voc,cold (V)</t>
         </is>
       </c>
-      <c r="B10">
-        <f>N_S*Voc_cold</f>
-        <v/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N_S*Voc_cold</t>
+        </is>
       </c>
       <c r="C10">
         <f>Parameters!B25*C3</f>
@@ -1000,9 +996,10 @@
           <t>String Vmp,hot (V)</t>
         </is>
       </c>
-      <c r="B11">
-        <f>N_S*Vmp_hot_ext</f>
-        <v/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N_S*Vmp_hot_ext</t>
+        </is>
       </c>
       <c r="C11">
         <f>Parameters!B25*C4</f>
@@ -1020,9 +1017,10 @@
           <t>String Vmp,cold (V)</t>
         </is>
       </c>
-      <c r="B12">
-        <f>N_S*Vmp_cold</f>
-        <v/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N_S*Vmp_cold</t>
+        </is>
       </c>
       <c r="C12">
         <f>Parameters!B25*C6</f>
@@ -1040,9 +1038,10 @@
           <t>I_chg (A)</t>
         </is>
       </c>
-      <c r="B13">
-        <f>MIN(P_PV*eta_MPPT*1000/V_bat_chg, I_ctrl_out_max)</f>
-        <v/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIN(P_PV*eta_MPPT*1000/V_bat_chg, I_ctrl_out_max)</t>
+        </is>
       </c>
       <c r="C13">
         <f>ROUND(MIN(C9*Parameters!B12*1000/Parameters!B10,Parameters!B11),1)</f>
@@ -1054,15 +1053,13 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
           <t>Monthly review (P_PV=3.00 kWp, tilt 30 deg)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
